--- a/Result/profitability/3419.xlsx
+++ b/Result/profitability/3419.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.42</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.41375</v>
+        <v>-0.4025</v>
       </c>
       <c r="N2" t="n">
-        <v>13.67375</v>
+        <v>12.91375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.61</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.42625</v>
+        <v>-0.4462499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>13.125</v>
+        <v>12.87125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -902,7 +902,7 @@
         <v>-0.36625</v>
       </c>
       <c r="N4" t="n">
-        <v>13.28125</v>
+        <v>13.31375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.295</v>
+        <v>-0.26375</v>
       </c>
       <c r="N5" t="n">
-        <v>13.93375</v>
+        <v>14.43125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.20125</v>
+        <v>-0.22</v>
       </c>
       <c r="N6" t="n">
-        <v>15.04125</v>
+        <v>15.0425</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.17125</v>
+        <v>-0.16875</v>
       </c>
       <c r="N7" t="n">
-        <v>15.95</v>
+        <v>15.9925</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.09874999999999998</v>
+        <v>-0.11125</v>
       </c>
       <c r="N8" t="n">
-        <v>16.50125</v>
+        <v>16.55375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-0.08</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.06874999999999998</v>
+        <v>-0.06874999999999996</v>
       </c>
       <c r="N9" t="n">
         <v>16.87375</v>
@@ -1645,7 +1645,7 @@
         <v>-0.18</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.03874999999999998</v>
+        <v>-0.03874999999999997</v>
       </c>
       <c r="N10" t="n">
         <v>16.77125</v>
@@ -1772,7 +1772,7 @@
         <v>0.19</v>
       </c>
       <c r="M11" t="n">
-        <v>0.06125000000000002</v>
+        <v>0.06125000000000003</v>
       </c>
       <c r="N11" t="n">
         <v>17.275</v>
@@ -1899,7 +1899,7 @@
         <v>-0.04</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02875000000000002</v>
+        <v>0.02875000000000003</v>
       </c>
       <c r="N12" t="n">
         <v>17.68375</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3419</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>463</v>
+      </c>
+      <c r="D75" t="n">
+        <v>404</v>
+      </c>
+      <c r="E75" t="n">
+        <v>58</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-49</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-10.55%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-50</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-50</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.41375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.9975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.09999999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.4199999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03445447087776876</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.373134328358209</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.979999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4611819235225953</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
